--- a/entorno/mir-v2/plantillas/DISP_PENAL_2026_T1_MODELO.xlsx
+++ b/entorno/mir-v2/plantillas/DISP_PENAL_2026_T1_MODELO.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CRC" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="CRSC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="MPT" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CAD" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Guardia Comisaría" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="INSTRUCCIONES" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="LISTAS" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRC" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRSC" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPT" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAD" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guardia Comisaría" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/entorno/mir-v2/plantillas/DISP_PENAL_2026_T1_MODELO.xlsx
+++ b/entorno/mir-v2/plantillas/DISP_PENAL_2026_T1_MODELO.xlsx
@@ -1,19 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRC" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRSC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPT" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAD" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guardia Comisaría" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet name="CRC" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CRSC" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MPT" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="CAD" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Guardia Comisaría" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Listas" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,10 +41,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
@@ -97,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -110,10 +105,6 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -193,304 +184,292 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>RUNAC</author>
+    <author>MIR</author>
   </authors>
   <commentList>
     <comment ref="A3" authorId="0" shapeId="0">
       <text>
         <t>Nombre del dispositvo
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="B3" authorId="0" shapeId="0">
       <text>
         <t>Dependencia institucional
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <t>Localidad
-Qué se espera: texto
-Máximo 120 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="D3" authorId="0" shapeId="0">
       <text>
         <t>Dirección
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="E3" authorId="0" shapeId="0">
       <text>
         <t>Teléfono
-Qué se espera: texto
-Máximo 50 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 50 caracteres.</t>
       </text>
     </comment>
     <comment ref="F3" authorId="0" shapeId="0">
       <text>
         <t>Capacidad de alojamiento mujeres (plazas disponibles)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.</t>
       </text>
     </comment>
     <comment ref="G3" authorId="0" shapeId="0">
       <text>
         <t>Capacidad de alojamiento varones (plazas disponibles)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <t>¿Cuenta con Proyecto Institucional?
-Qué se espera: texto
-Máximo 38 caracteres.
-Elegir de la lista "Cuenta con Proyecto Institucional".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, es una herramienta de gestión, Sí, está actualizado pero no se aplica, Sí, pero está desactualizado, No, pero se encuentra en diseño, No.</t>
       </text>
     </comment>
     <comment ref="I3" authorId="0" shapeId="0">
       <text>
         <t>¿Cuenta con Normativa Convivencial?
-Qué se espera: texto
-Máximo 38 caracteres.
-Elegir de la lista "Cuenta con Normativa Convivencial".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, es una herramienta de gestión, Sí, está actualizada pero no se aplica, Sí, pero está desactualizada, No, pero se encuentra en diseño, No.</t>
       </text>
     </comment>
     <comment ref="J3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de agentes: equipo técnico y profesional (incluye cuidadores)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 10 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad agentes de salud
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de personal: administrativo, limpieza, cocina y mantenimiento
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 10 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="M3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de personal seguridad
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="N3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolos de ingreso
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="O3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolo de requisa
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="P3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolo de denuncias por malos tratos
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="Q3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolos de actuación ante conflictos entre pares
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="R3" authorId="0" shapeId="0">
       <text>
         <t>Protocolo de abordaje del suicidio
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolo de sanciones
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="T3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de horas semanales destinadas al contacto presencial, afectivo/familiar
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Entre 0 y 168.</t>
       </text>
     </comment>
     <comment ref="U3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con espacios para visitas socioafectivas
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="V3" authorId="0" shapeId="0">
       <text>
         <t>Cumple con los niveles de obligatoriedad de educación primaria
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Cumple con los niveles de obligatoriedad de educación primaria".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, con convenio ME, Sí, sin convenio ME, No.</t>
       </text>
     </comment>
     <comment ref="W3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de horas semanales dedicadas a la educación primaria
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Entre 0 y 168.</t>
       </text>
     </comment>
     <comment ref="X3" authorId="0" shapeId="0">
       <text>
         <t>Cumple con los niveles de obligatoriedad de educación secundaria
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Cumple con los niveles de obligatoriedad de educación primaria".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, con convenio ME, Sí, sin convenio ME, No.</t>
       </text>
     </comment>
     <comment ref="Y3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de horas semanales dedicadas a la educación secundaria
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Entre 0 y 168.</t>
       </text>
     </comment>
     <comment ref="Z3" authorId="0" shapeId="0">
       <text>
         <t>Tiene aulas destinadas a la educación obligatoria
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AA3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de horas semanales dedicadas a la formación profesional
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Entre 0 y 168.</t>
       </text>
     </comment>
     <comment ref="AB3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de horas semanales dedicadas a talleres deportivos y culturales
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Entre 0 y 168.</t>
       </text>
     </comment>
     <comment ref="AC3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con espacio para talleres
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AD3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con asesoramiento técnico jurídico
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AE3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con patio abierto
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AF3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con patio techado
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AG3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con celdas secas
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AH3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con celdas humedas
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AI3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con mobiliario en las celdas
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AJ3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con colchones ignífugos
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
   </commentList>
@@ -500,304 +479,292 @@
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>RUNAC</author>
+    <author>MIR</author>
   </authors>
   <commentList>
     <comment ref="A3" authorId="0" shapeId="0">
       <text>
         <t>Nombre del dispositvo
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="B3" authorId="0" shapeId="0">
       <text>
         <t>Dependencia institucional
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <t>Localidad
-Qué se espera: texto
-Máximo 120 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="D3" authorId="0" shapeId="0">
       <text>
         <t>Dirección
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="E3" authorId="0" shapeId="0">
       <text>
         <t>Teléfono
-Qué se espera: texto
-Máximo 50 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 50 caracteres.</t>
       </text>
     </comment>
     <comment ref="F3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con Proyecto Institucional
-Qué se espera: texto
-Máximo 38 caracteres.
-Elegir de la lista "Cuenta con Proyecto Institucional".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, es una herramienta de gestión, Sí, está actualizado pero no se aplica, Sí, pero está desactualizado, No, pero se encuentra en diseño, No.</t>
       </text>
     </comment>
     <comment ref="G3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con Normativa Convivencial
-Qué se espera: texto
-Máximo 38 caracteres.
-Elegir de la lista "Cuenta con Normativa Convivencial".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, es una herramienta de gestión, Sí, está actualizada pero no se aplica, Sí, pero está desactualizada, No, pero se encuentra en diseño, No.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolos de ingreso
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="I3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolo de requisa
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="J3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolo de denuncias por malos tratos
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolos de actuación ante conflictos entre pares
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>Protocolo de abordaje del suicidio
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="M3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolo de sanciones
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="N3" authorId="0" shapeId="0">
       <text>
         <t>Capacidad de alojamiento mujeres (plazas disponibles)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.</t>
       </text>
     </comment>
     <comment ref="O3" authorId="0" shapeId="0">
       <text>
         <t>Capacidad de alojamiento varones (plazas disponibles)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.</t>
       </text>
     </comment>
     <comment ref="P3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de agentes: equipo técnico y profesional (incluye cuidadores)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="Q3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad agentes de salud
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="R3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de personal: administrativo, limpieza, cocina y mantenimiento
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de personal seguridad
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="T3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de horas semanales destinadas al contacto presencial, afectivo/familiar
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Entre 0 y 168.</t>
       </text>
     </comment>
     <comment ref="U3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con espacios para visitas socioafectivas
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="V3" authorId="0" shapeId="0">
       <text>
         <t>Cumple con los niveles de obligatoriedad de educación primaria
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Cumple con los niveles de obligatoriedad de educación primaria".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, con convenio ME, Sí, sin convenio ME, No.</t>
       </text>
     </comment>
     <comment ref="W3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de horas semanales dedicadas a la educación primaria
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Entre 0 y 168.</t>
       </text>
     </comment>
     <comment ref="X3" authorId="0" shapeId="0">
       <text>
         <t>Cumple con los niveles de obligatoriedad de educación secundaria
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Cumple con los niveles de obligatoriedad de educación primaria".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, con convenio ME, Sí, sin convenio ME, No.</t>
       </text>
     </comment>
     <comment ref="Y3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de horas semanales dedicadas a la educación secundaria
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Entre 0 y 168.</t>
       </text>
     </comment>
     <comment ref="Z3" authorId="0" shapeId="0">
       <text>
         <t>Tiene aulas destinadas a la educación obligatoria
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AA3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de horas semanales dedicadas a la formación profesional
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Entre 0 y 168.</t>
       </text>
     </comment>
     <comment ref="AB3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de horas semanales dedicadas a talleres deportivos y culturales
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Entre 0 y 168.</t>
       </text>
     </comment>
     <comment ref="AC3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con espacio para talleres
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AD3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con asesoramiento técnico jurídico
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AE3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con patio abierto
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AF3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con patio techado
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AG3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con celdas secas
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AH3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con celdas humedas
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AI3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con mobiliario en las celdas
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AJ3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con colchones ignífugos
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
   </commentList>
@@ -807,89 +774,82 @@
 <file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>RUNAC</author>
+    <author>MIR</author>
   </authors>
   <commentList>
     <comment ref="A3" authorId="0" shapeId="0">
       <text>
         <t>Nombre del dispositvo
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="B3" authorId="0" shapeId="0">
       <text>
         <t>Dependencia institucional
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <t>Localidad
-Qué se espera: texto
-Máximo 120 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="D3" authorId="0" shapeId="0">
       <text>
         <t>Dirección
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="E3" authorId="0" shapeId="0">
       <text>
         <t>Teléfono
-Qué se espera: texto
-Máximo 50 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 50 caracteres.</t>
       </text>
     </comment>
     <comment ref="F3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con Proyecto Institucional
-Qué se espera: texto
-Máximo 38 caracteres.
-Elegir de la lista "Cuenta con Proyecto Institucional".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, es una herramienta de gestión, Sí, está actualizado pero no se aplica, Sí, pero está desactualizado, No, pero se encuentra en diseño, No.</t>
       </text>
     </comment>
     <comment ref="G3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con espacio de grupalidad
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de agentes: equipo técnico y profesional (incluye cuidadores)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="I3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con asesoramiento técnico jurídico
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="J3" authorId="0" shapeId="0">
       <text>
         <t>Jurisdicciones dentro de la provincia en las que el dispositivo tiene alcance
-Qué se espera: texto
-Máximo 120 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
   </commentList>
@@ -899,230 +859,218 @@
 <file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>RUNAC</author>
+    <author>MIR</author>
   </authors>
   <commentList>
     <comment ref="A3" authorId="0" shapeId="0">
       <text>
         <t>Nombre del dispositvo
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="B3" authorId="0" shapeId="0">
       <text>
         <t>Dependencia institucional
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <t>Localidad
-Qué se espera: texto
-Máximo 120 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="D3" authorId="0" shapeId="0">
       <text>
         <t>Dirección
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="E3" authorId="0" shapeId="0">
       <text>
         <t>Teléfono
-Qué se espera: texto
-Máximo 50 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 50 caracteres.</t>
       </text>
     </comment>
     <comment ref="F3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con Proyecto Institucional
-Qué se espera: texto
-Máximo 38 caracteres.
-Elegir de la lista "Cuenta con Proyecto Institucional".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, es una herramienta de gestión, Sí, está actualizado pero no se aplica, Sí, pero está desactualizado, No, pero se encuentra en diseño, No.</t>
       </text>
     </comment>
     <comment ref="G3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con resolución de creación
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con Normativa Convivencial
-Qué se espera: texto
-Máximo 38 caracteres.
-Elegir de la lista "Cuenta con Normativa Convivencial".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, es una herramienta de gestión, Sí, está actualizada pero no se aplica, Sí, pero está desactualizada, No, pero se encuentra en diseño, No.</t>
       </text>
     </comment>
     <comment ref="I3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolos de articulación interministerial. Con qué áreas
-Qué se espera: texto
-Máximo 34 caracteres.
-Elegir de la lista "Cuenta con protocolos de articulación interministerial. Con qué áreas".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, con áreas de salud y seguridad, Sí, con áreas de seguridad, Sí, con áreas de salud, No.</t>
       </text>
     </comment>
     <comment ref="J3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolos de ingreso
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolo de requisa
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolo de denuncias por malos tratos
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="M3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolos de actuación ante conflictos entre pares
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="N3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolo de abordaje del suicidio
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="O3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolo de sanciones
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="P3" authorId="0" shapeId="0">
       <text>
         <t>Capacidad de alojamiento mujeres (plazas disponibles)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.</t>
       </text>
     </comment>
     <comment ref="Q3" authorId="0" shapeId="0">
       <text>
         <t>Capacidad de alojamiento varones (plazas disponibles)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.</t>
       </text>
     </comment>
     <comment ref="R3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de agentes: equipo técnico y profesional (incluye cuidadores)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad agentes de salud
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="T3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de personal: administrativo, limpieza, cocina y mantenimiento
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="U3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de personal seguridad
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="V3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con celdas secas
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="W3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con celdas humedas
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="X3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con mobiliario en las celdas
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="Y3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con colchones ignífugos
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="Z3" authorId="0" shapeId="0">
       <text>
         <t>Jurisdicciones dentro de la provincia en las que tiene alcancce territorial el dispositivo
-Qué se espera: texto
-Máximo 120 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="AA3" authorId="0" shapeId="0">
       <text>
         <t>Tiempo máximo de permanencia dentro del dispositivo (en horas)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.</t>
       </text>
     </comment>
   </commentList>
@@ -1132,80 +1080,75 @@
 <file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>RUNAC</author>
+    <author>MIR</author>
   </authors>
   <commentList>
     <comment ref="A3" authorId="0" shapeId="0">
       <text>
         <t>Nombre del dispositvo
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="B3" authorId="0" shapeId="0">
       <text>
         <t>Dependencia institucional
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <t>Teléfono
-Qué se espera: texto
-Máximo 50 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 50 caracteres.</t>
       </text>
     </comment>
     <comment ref="D3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con resolución de creación
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="E3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolos de articulación interministerial. Con qué áreas
-Qué se espera: texto
-Máximo 34 caracteres.
-Elegir de la lista "Cuenta con protocolos de articulación interministerial. Con qué áreas".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, con áreas de salud y seguridad, Sí, con áreas de seguridad, Sí, con áreas de salud, No.</t>
       </text>
     </comment>
     <comment ref="F3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolo de denuncias por malos tratos
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="G3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de agentes: equipo técnico y profesional (incluye cuidadores)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <t>Jurisdicciones dentro de la provincia en las que tiene alcancce territorial el dispositivo
-Qué se espera: texto
-Máximo 120 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="I3" authorId="0" shapeId="0">
       <text>
         <t>Tiempo máximo de permanencia dentro del dispositivo (en horas)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.</t>
       </text>
     </comment>
   </commentList>
@@ -4338,64 +4281,64 @@
   </mergeCells>
   <dataValidations count="20">
     <dataValidation sqref="H4:H203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Cuenta con Proyecto Institucional?&quot;." type="list">
-      <formula1>LISTAS!$C$2:$C$6</formula1>
+      <formula1>Listas!$C$2:$C$6</formula1>
     </dataValidation>
     <dataValidation sqref="I4:I203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Cuenta con Normativa Convivencial?&quot;." type="list">
-      <formula1>LISTAS!$A$2:$A$6</formula1>
+      <formula1>Listas!$A$2:$A$6</formula1>
     </dataValidation>
     <dataValidation sqref="N4:N203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolos de ingreso&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="O4:O203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolo de requisa&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="P4:P203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolo de denuncias por malos tratos&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="Q4:Q203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolos de actuación ante conflictos entre pares&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="R4:R203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Protocolo de abordaje del suicidio&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="S4:S203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolo de sanciones&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="U4:U203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con espacios para visitas socioafectivas&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="V4:V203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cumple con los niveles de obligatoriedad de educación primaria&quot;." type="list">
-      <formula1>LISTAS!$D$2:$D$4</formula1>
+      <formula1>Listas!$D$2:$D$4</formula1>
     </dataValidation>
     <dataValidation sqref="X4:X203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cumple con los niveles de obligatoriedad de educación secundaria&quot;." type="list">
-      <formula1>LISTAS!$D$2:$D$4</formula1>
+      <formula1>Listas!$D$2:$D$4</formula1>
     </dataValidation>
     <dataValidation sqref="Z4:Z203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Tiene aulas destinadas a la educación obligatoria&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AC4:AC203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con espacio para talleres&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AD4:AD203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con asesoramiento técnico jurídico&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AE4:AE203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con patio abierto&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AF4:AF203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con patio techado&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AG4:AG203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con celdas secas&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AH4:AH203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con celdas humedas&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AI4:AI203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con mobiliario en las celdas&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AJ4:AJ203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con colchones ignífugos&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7246,64 +7189,64 @@
   </mergeCells>
   <dataValidations count="20">
     <dataValidation sqref="F4:F203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con Proyecto Institucional&quot;." type="list">
-      <formula1>LISTAS!$C$2:$C$6</formula1>
+      <formula1>Listas!$C$2:$C$6</formula1>
     </dataValidation>
     <dataValidation sqref="G4:G203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con Normativa Convivencial&quot;." type="list">
-      <formula1>LISTAS!$A$2:$A$6</formula1>
+      <formula1>Listas!$A$2:$A$6</formula1>
     </dataValidation>
     <dataValidation sqref="H4:H203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolos de ingreso&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="I4:I203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolo de requisa&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="J4:J203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolo de denuncias por malos tratos&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="K4:K203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolos de actuación ante conflictos entre pares&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="L4:L203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Protocolo de abordaje del suicidio&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="M4:M203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolo de sanciones&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="U4:U203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con espacios para visitas socioafectivas&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="V4:V203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cumple con los niveles de obligatoriedad de educación primaria&quot;." type="list">
-      <formula1>LISTAS!$D$2:$D$4</formula1>
+      <formula1>Listas!$D$2:$D$4</formula1>
     </dataValidation>
     <dataValidation sqref="X4:X203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cumple con los niveles de obligatoriedad de educación secundaria&quot;." type="list">
-      <formula1>LISTAS!$D$2:$D$4</formula1>
+      <formula1>Listas!$D$2:$D$4</formula1>
     </dataValidation>
     <dataValidation sqref="Z4:Z203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Tiene aulas destinadas a la educación obligatoria&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AC4:AC203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con espacio para talleres&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AD4:AD203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con asesoramiento técnico jurídico&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AE4:AE203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con patio abierto&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AF4:AF203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con patio techado&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AG4:AG203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con celdas secas&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AH4:AH203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con celdas humedas&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AI4:AI203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con mobiliario en las celdas&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AJ4:AJ203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con colchones ignífugos&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7998,13 +7941,13 @@
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="F4:F203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con Proyecto Institucional&quot;." type="list">
-      <formula1>LISTAS!$C$2:$C$6</formula1>
+      <formula1>Listas!$C$2:$C$6</formula1>
     </dataValidation>
     <dataValidation sqref="G4:G203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con espacio de grupalidad&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="I4:I203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con asesoramiento técnico jurídico&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10001,46 +9944,46 @@
   </mergeCells>
   <dataValidations count="14">
     <dataValidation sqref="F4:F203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con Proyecto Institucional&quot;." type="list">
-      <formula1>LISTAS!$C$2:$C$6</formula1>
+      <formula1>Listas!$C$2:$C$6</formula1>
     </dataValidation>
     <dataValidation sqref="G4:G203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con resolución de creación&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="H4:H203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con Normativa Convivencial&quot;." type="list">
-      <formula1>LISTAS!$A$2:$A$6</formula1>
+      <formula1>Listas!$A$2:$A$6</formula1>
     </dataValidation>
     <dataValidation sqref="I4:I203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolos de articulación interministerial. Con qué áreas&quot;." type="list">
-      <formula1>LISTAS!$B$2:$B$5</formula1>
+      <formula1>Listas!$B$2:$B$5</formula1>
     </dataValidation>
     <dataValidation sqref="J4:J203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolos de ingreso&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="K4:K203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolo de requisa&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="L4:L203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolo de denuncias por malos tratos&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="M4:M203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolos de actuación ante conflictos entre pares&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="N4:N203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolo de abordaje del suicidio&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="O4:O203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolo de sanciones&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="V4:V203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con celdas secas&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="W4:W203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con celdas humedas&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="X4:X203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con mobiliario en las celdas&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="Y4:Y203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con colchones ignífugos&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10929,13 +10872,13 @@
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="D4:D203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con resolución de creación&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="E4:E203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolos de articulación interministerial. Con qué áreas&quot;." type="list">
-      <formula1>LISTAS!$B$2:$B$5</formula1>
+      <formula1>Listas!$B$2:$B$5</formula1>
     </dataValidation>
     <dataValidation sqref="F4:F203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolo de denuncias por malos tratos&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10944,1275 +10887,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B128"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Campo</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Indicación para el llenado</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Hoja: CRC</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Nombre del dispositvo</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Dependencia institucional</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Localidad</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Dirección</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Teléfono</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Capacidad de alojamiento mujeres (plazas disponibles)</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Capacidad de alojamiento varones (plazas disponibles)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>¿Cuenta con Proyecto Institucional?</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cuenta con Proyecto Institucional".</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>¿Cuenta con Normativa Convivencial?</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cuenta con Normativa Convivencial".</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Cantidad de agentes: equipo técnico y profesional (incluye cuidadores)</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Cantidad agentes de salud</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Cantidad de personal: administrativo, limpieza, cocina y mantenimiento</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Cantidad de personal seguridad</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolos de ingreso</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolo de requisa</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolo de denuncias por malos tratos</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolos de actuación ante conflictos entre pares</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Protocolo de abordaje del suicidio</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolo de sanciones</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Cantidad de horas semanales destinadas al contacto presencial, afectivo/familiar</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Cuenta con espacios para visitas socioafectivas</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Cumple con los niveles de obligatoriedad de educación primaria</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cumple con los niveles de obligatoriedad de educación primaria".</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Cantidad de horas semanales dedicadas a la educación primaria</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Cumple con los niveles de obligatoriedad de educación secundaria</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cumple con los niveles de obligatoriedad de educación primaria".</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Cantidad de horas semanales dedicadas a la educación secundaria</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Tiene aulas destinadas a la educación obligatoria</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Cantidad de horas semanales dedicadas a la formación profesional</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Cantidad de horas semanales dedicadas a talleres deportivos y culturales</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Cuenta con espacio para talleres</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Cuenta con asesoramiento técnico jurídico</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Cuenta con patio abierto</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Cuenta con patio techado</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Cuenta con celdas secas</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Cuenta con celdas humedas</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Cuenta con mobiliario en las celdas</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Cuenta con colchones ignífugos</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>Hoja: CRSC</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Nombre del dispositvo</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Dependencia institucional</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Localidad</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Dirección</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Teléfono</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Cuenta con Proyecto Institucional</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cuenta con Proyecto Institucional".</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Cuenta con Normativa Convivencial</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cuenta con Normativa Convivencial".</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolos de ingreso</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolo de requisa</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolo de denuncias por malos tratos</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolos de actuación ante conflictos entre pares</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Protocolo de abordaje del suicidio</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolo de sanciones</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Capacidad de alojamiento mujeres (plazas disponibles)</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Capacidad de alojamiento varones (plazas disponibles)</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Cantidad de agentes: equipo técnico y profesional (incluye cuidadores)</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Cantidad agentes de salud</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Cantidad de personal: administrativo, limpieza, cocina y mantenimiento</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Cantidad de personal seguridad</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Cantidad de horas semanales destinadas al contacto presencial, afectivo/familiar</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Cuenta con espacios para visitas socioafectivas</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Cumple con los niveles de obligatoriedad de educación primaria</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cumple con los niveles de obligatoriedad de educación primaria".</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Cantidad de horas semanales dedicadas a la educación primaria</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Cumple con los niveles de obligatoriedad de educación secundaria</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cumple con los niveles de obligatoriedad de educación primaria".</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Cantidad de horas semanales dedicadas a la educación secundaria</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Tiene aulas destinadas a la educación obligatoria</t>
-        </is>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Cantidad de horas semanales dedicadas a la formación profesional</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Cantidad de horas semanales dedicadas a talleres deportivos y culturales</t>
-        </is>
-      </c>
-      <c r="B68" s="7" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Cuenta con espacio para talleres</t>
-        </is>
-      </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Cuenta con asesoramiento técnico jurídico</t>
-        </is>
-      </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Cuenta con patio abierto</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Cuenta con patio techado</t>
-        </is>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Cuenta con celdas secas</t>
-        </is>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Cuenta con celdas humedas</t>
-        </is>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Cuenta con mobiliario en las celdas</t>
-        </is>
-      </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Cuenta con colchones ignífugos</t>
-        </is>
-      </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>Hoja: MPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Nombre del dispositvo</t>
-        </is>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Dependencia institucional</t>
-        </is>
-      </c>
-      <c r="B80" s="7" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Localidad</t>
-        </is>
-      </c>
-      <c r="B81" s="7" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Dirección</t>
-        </is>
-      </c>
-      <c r="B82" s="7" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Teléfono</t>
-        </is>
-      </c>
-      <c r="B83" s="7" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Cuenta con Proyecto Institucional</t>
-        </is>
-      </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cuenta con Proyecto Institucional".</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Cuenta con espacio de grupalidad</t>
-        </is>
-      </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Cantidad de agentes: equipo técnico y profesional (incluye cuidadores)</t>
-        </is>
-      </c>
-      <c r="B86" s="7" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Cuenta con asesoramiento técnico jurídico</t>
-        </is>
-      </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Jurisdicciones dentro de la provincia en las que el dispositivo tiene alcance</t>
-        </is>
-      </c>
-      <c r="B88" s="7" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>Hoja: CAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Nombre del dispositvo</t>
-        </is>
-      </c>
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Dependencia institucional</t>
-        </is>
-      </c>
-      <c r="B92" s="7" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Localidad</t>
-        </is>
-      </c>
-      <c r="B93" s="7" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Dirección</t>
-        </is>
-      </c>
-      <c r="B94" s="7" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Teléfono</t>
-        </is>
-      </c>
-      <c r="B95" s="7" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Cuenta con Proyecto Institucional</t>
-        </is>
-      </c>
-      <c r="B96" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cuenta con Proyecto Institucional".</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Cuenta con resolución de creación</t>
-        </is>
-      </c>
-      <c r="B97" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Cuenta con Normativa Convivencial</t>
-        </is>
-      </c>
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cuenta con Normativa Convivencial".</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolos de articulación interministerial. Con qué áreas</t>
-        </is>
-      </c>
-      <c r="B99" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cuenta con protocolos de articulación interministerial. Con qué áreas".</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolos de ingreso</t>
-        </is>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolo de requisa</t>
-        </is>
-      </c>
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolo de denuncias por malos tratos</t>
-        </is>
-      </c>
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolos de actuación ante conflictos entre pares</t>
-        </is>
-      </c>
-      <c r="B103" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolo de abordaje del suicidio</t>
-        </is>
-      </c>
-      <c r="B104" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolo de sanciones</t>
-        </is>
-      </c>
-      <c r="B105" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Capacidad de alojamiento mujeres (plazas disponibles)</t>
-        </is>
-      </c>
-      <c r="B106" s="7" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Capacidad de alojamiento varones (plazas disponibles)</t>
-        </is>
-      </c>
-      <c r="B107" s="7" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Cantidad de agentes: equipo técnico y profesional (incluye cuidadores)</t>
-        </is>
-      </c>
-      <c r="B108" s="7" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Cantidad agentes de salud</t>
-        </is>
-      </c>
-      <c r="B109" s="7" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Cantidad de personal: administrativo, limpieza, cocina y mantenimiento</t>
-        </is>
-      </c>
-      <c r="B110" s="7" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Cantidad de personal seguridad</t>
-        </is>
-      </c>
-      <c r="B111" s="7" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Cuenta con celdas secas</t>
-        </is>
-      </c>
-      <c r="B112" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Cuenta con celdas humedas</t>
-        </is>
-      </c>
-      <c r="B113" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Cuenta con mobiliario en las celdas</t>
-        </is>
-      </c>
-      <c r="B114" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Cuenta con colchones ignífugos</t>
-        </is>
-      </c>
-      <c r="B115" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Jurisdicciones dentro de la provincia en las que tiene alcancce territorial el dispositivo</t>
-        </is>
-      </c>
-      <c r="B116" s="7" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Tiempo máximo de permanencia dentro del dispositivo (en horas)</t>
-        </is>
-      </c>
-      <c r="B117" s="7" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>Hoja: Guardia Comisaría</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Nombre del dispositvo</t>
-        </is>
-      </c>
-      <c r="B120" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Dependencia institucional</t>
-        </is>
-      </c>
-      <c r="B121" s="7" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Teléfono</t>
-        </is>
-      </c>
-      <c r="B122" s="7" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Cuenta con resolución de creación</t>
-        </is>
-      </c>
-      <c r="B123" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolos de articulación interministerial. Con qué áreas</t>
-        </is>
-      </c>
-      <c r="B124" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cuenta con protocolos de articulación interministerial. Con qué áreas".</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolo de denuncias por malos tratos</t>
-        </is>
-      </c>
-      <c r="B125" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Cantidad de agentes: equipo técnico y profesional (incluye cuidadores)</t>
-        </is>
-      </c>
-      <c r="B126" s="7" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Jurisdicciones dentro de la provincia en las que tiene alcancce territorial el dispositivo</t>
-        </is>
-      </c>
-      <c r="B127" s="7" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Tiempo máximo de permanencia dentro del dispositivo (en horas)</t>
-        </is>
-      </c>
-      <c r="B128" s="7" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
